--- a/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/home_prices.xlsx
+++ b/ML_Topics_Codes_Saifur/Linear_Regression/Simple_Linear_Regression/home_prices.xlsx
@@ -40,6 +40,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -61,6 +62,7 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,12 +107,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -237,7 +247,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -249,43 +259,67 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>550000</v>
+      <c r="B2" s="2" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>565000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="2" t="n">
         <v>3200</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>610000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="2" t="n">
         <v>3600</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>680000</v>
+      <c r="B5" s="2" t="n">
+        <v>740000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>725000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>2700</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>580000</v>
       </c>
     </row>
   </sheetData>
